--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487151_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487151_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9419</v>
+        <v>1.9137</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0635</v>
+        <v>2.8212</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1216</v>
+        <v>-0.9075</v>
       </c>
       <c r="G2" t="n">
         <v>-2.5409</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6988</v>
+        <v>0.6706</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9711</v>
+        <v>0.7288</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2723</v>
+        <v>-0.0582</v>
       </c>
       <c r="V2" t="n">
         <v>3.398</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5549</v>
+        <v>0.8429</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9255</v>
+        <v>-0.1423</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3706</v>
+        <v>0.9852</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.013</v>
+        <v>-0.2582</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.883</v>
+        <v>0.1945</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.13</v>
+        <v>-0.4527</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2257</v>
+        <v>0.676</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3885</v>
+        <v>0.7088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1628</v>
+        <v>-0.0328</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7873</v>
+        <v>-0.9341</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4945</v>
+        <v>-0.5143</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2928</v>
+        <v>-0.4199</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R3" t="n">
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8608</v>
+        <v>-0.1342</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8304</v>
+        <v>0.3398</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0304</v>
+        <v>-0.4739</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0649</v>
+        <v>0.6562</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3508</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.178</v>
+        <v>0.2125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1393</v>
+        <v>1.2953</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0387</v>
+        <v>-1.0827</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2582</v>
+        <v>0.9329</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1945</v>
+        <v>-0.7472</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4527</v>
+        <v>1.6801</v>
       </c>
       <c r="J4" t="n">
-        <v>0.676</v>
+        <v>2.295</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7088</v>
+        <v>1.009</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0328</v>
+        <v>1.286</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9341</v>
+        <v>-1.3621</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5143</v>
+        <v>-1.7562</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4199</v>
+        <v>0.3941</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>0.201</v>
+        <v>-0.5975</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6214</v>
+        <v>-0.0347</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4204</v>
+        <v>-0.5628</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>-0.1228</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3209</v>
+        <v>-0.1612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7351</v>
+        <v>-1.3302</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0559</v>
+        <v>1.169</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9329</v>
+        <v>2.5697</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7472</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6801</v>
+        <v>2.579</v>
       </c>
       <c r="J5" t="n">
-        <v>2.295</v>
+        <v>2.3354</v>
       </c>
       <c r="K5" t="n">
-        <v>1.009</v>
+        <v>-0.2693</v>
       </c>
       <c r="L5" t="n">
-        <v>1.286</v>
+        <v>2.6047</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3621</v>
+        <v>0.2343</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7562</v>
+        <v>0.26</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3941</v>
+        <v>-0.0257</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>-1.158</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.131</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5949</v>
+        <v>-0.1143</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5361</v>
+        <v>-0.6795</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1228</v>
+        <v>-0.779</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1228</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3292</v>
+        <v>-0.549</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3911</v>
+        <v>-0.0178</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0619</v>
+        <v>-0.5312</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5697</v>
+        <v>-1.013</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.883</v>
       </c>
       <c r="I6" t="n">
-        <v>2.579</v>
+        <v>-0.13</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3354</v>
+        <v>-0.2257</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2693</v>
+        <v>-0.3885</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6047</v>
+        <v>0.1628</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2343</v>
+        <v>-0.7873</v>
       </c>
       <c r="N6" t="n">
-        <v>0.26</v>
+        <v>-0.4945</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0257</v>
+        <v>-0.2928</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9618</v>
+        <v>0.7568</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1752</v>
+        <v>0.8871</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7866</v>
+        <v>-0.1303</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.779</v>
+        <v>-1.0649</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1228</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.123</v>
+        <v>-1.4079</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5765</v>
+        <v>0.0726</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5465</v>
+        <v>-1.4806</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.9261</v>
+        <v>-0.3173</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1725</v>
+        <v>-0.3694</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7536</v>
+        <v>0.0521</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4712</v>
+        <v>0.6239</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1439</v>
+        <v>0.5589</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3273</v>
+        <v>0.065</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4549</v>
+        <v>-0.9411</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0286</v>
+        <v>-0.9283</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4263</v>
+        <v>-0.0129</v>
       </c>
       <c r="P7" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8811</v>
+        <v>0.3074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4032</v>
+        <v>0.3209</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4779</v>
+        <v>-0.0136</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7192</v>
+        <v>-2.1701</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7368</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1903</v>
+        <v>-1.5895</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.014</v>
+        <v>-2.4131</v>
       </c>
       <c r="F8" t="n">
         <v>0.8236</v>
@@ -1078,10 +1078,10 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.386</v>
+        <v>0.2148</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2102</v>
+        <v>0.3907</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1759</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2884</v>
+        <v>-1.7096</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8881</v>
+        <v>-0.9757</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4003</v>
+        <v>-0.7339</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3173</v>
+        <v>-3.9261</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3694</v>
+        <v>-2.1725</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0521</v>
+        <v>-1.7536</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6239</v>
+        <v>-2.4712</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5589</v>
+        <v>-1.1439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.065</v>
+        <v>-1.3273</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9411</v>
+        <v>-1.4549</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9283</v>
+        <v>-1.0286</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0129</v>
+        <v>-0.4263</v>
       </c>
       <c r="P9" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.4676</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6398</v>
+        <v>0.1977</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0667</v>
+        <v>-0.6653</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1701</v>
+        <v>1.7192</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4559</v>
+        <v>-0.7368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7119</v>
+        <v>-2.6739</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9919</v>
+        <v>-2.3639</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7038</v>
+        <v>-0.3099</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2332</v>
+        <v>-3.605</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1262</v>
+        <v>-1.2638</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3595</v>
+        <v>-2.3413</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6333</v>
+        <v>-2.7444</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2795</v>
+        <v>-0.823</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9129</v>
+        <v>-1.9214</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4001</v>
+        <v>-0.8607</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1533</v>
+        <v>-0.4408</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5534</v>
+        <v>-0.4199</v>
       </c>
       <c r="P10" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0034</v>
+        <v>0.5149</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0727</v>
+        <v>0.5734</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0761</v>
+        <v>-0.0585</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.5208</v>
+        <v>-1.5138</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8067</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4274</v>
+        <v>-2.9995</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9836</v>
+        <v>1.6508</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4438</v>
+        <v>-4.6503</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.605</v>
+        <v>1.2332</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2638</v>
+        <v>-0.1262</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3413</v>
+        <v>1.3595</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7444</v>
+        <v>1.6333</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.823</v>
+        <v>-0.2795</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9214</v>
+        <v>1.9129</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8607</v>
+        <v>-0.4001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4408</v>
+        <v>0.1533</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4199</v>
+        <v>-0.5534</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2386</v>
+        <v>-1.2909</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0462</v>
+        <v>-0.2683</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1924</v>
+        <v>-1.0226</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5138</v>
+        <v>-3.5208</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>-3.8067</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.7163</v>
+        <v>-8.121500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.998</v>
+        <v>-1.4031</v>
       </c>
       <c r="F12" t="n">
         <v>-6.718299999999999</v>
@@ -1360,13 +1360,13 @@
         <v>-5.941199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="J12" t="n">
         <v>1.2314</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9643999999999999</v>
+        <v>-0.9644000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>2.1959</v>
@@ -1390,10 +1390,10 @@
         <v>16.4058</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.414400000000001</v>
+        <v>-0.8195999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4261</v>
+        <v>3.0211</v>
       </c>
       <c r="U12" t="n">
         <v>-3.8406</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4835</v>
+        <v>9.2652</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4206</v>
+        <v>9.8184</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.5532</v>
       </c>
       <c r="G13" t="n">
         <v>1.4628</v>
@@ -1468,13 +1468,13 @@
         <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9857</v>
+        <v>1.7675</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9639</v>
+        <v>1.3617</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0218</v>
+        <v>0.4058</v>
       </c>
       <c r="V13" t="n">
         <v>4.2979</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7331</v>
+        <v>5.9345</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3966</v>
+        <v>4.5983</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3365</v>
+        <v>1.3362</v>
       </c>
       <c r="G14" t="n">
         <v>3.5334</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9631</v>
+        <v>0.2383</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0417</v>
+        <v>0.16</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0786</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.7418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2133</v>
+        <v>1.5461</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4594</v>
+        <v>0.6583</v>
       </c>
       <c r="F15" t="n">
-        <v>0.754</v>
+        <v>0.8878</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0717</v>
@@ -1624,13 +1624,13 @@
         <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7649</v>
+        <v>0.9637</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4449</v>
+        <v>-0.311</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4379</v>
+        <v>0.1781</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9016</v>
+        <v>0.3649</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3396</v>
+        <v>-0.1868</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5364</v>
+        <v>0.5202</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8227</v>
+        <v>0.4338</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3591</v>
+        <v>0.0864</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3826</v>
+        <v>1.5546</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2629</v>
+        <v>0.7813</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6454</v>
+        <v>0.7733</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1538</v>
+        <v>-1.0345</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4401</v>
+        <v>-0.3476</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2863</v>
+        <v>-0.6869</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7371</v>
+        <v>-0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7231</v>
+        <v>0.43</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6954</v>
+        <v>0.7403</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0277</v>
+        <v>-0.3104</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1164</v>
+        <v>-0.0464</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3649</v>
+        <v>-1.2662</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4812</v>
+        <v>1.2198</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5202</v>
+        <v>0.1357</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4338</v>
+        <v>-0.3869</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0864</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5546</v>
+        <v>0.2356</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7813</v>
+        <v>-0.4399</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7733</v>
+        <v>0.6755</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0345</v>
+        <v>-0.0998</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3476</v>
+        <v>0.053</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6869</v>
+        <v>-0.1528</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1355</v>
+        <v>0.1038</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7403</v>
+        <v>0.4283</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6048</v>
+        <v>-0.3246</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1291</v>
+        <v>-0.1023</v>
       </c>
       <c r="E18" t="n">
         <v>0.1335</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2626</v>
+        <v>-0.2358</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0134</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>0.1335</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9552</v>
+        <v>-0.1504</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6667</v>
+        <v>-1.3022</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7115</v>
+        <v>1.1519</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1357</v>
+        <v>1.5364</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3869</v>
+        <v>-0.8227</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5227000000000001</v>
+        <v>2.3591</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2356</v>
+        <v>1.3826</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4399</v>
+        <v>-1.2629</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6755</v>
+        <v>2.6454</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0998</v>
+        <v>0.1538</v>
       </c>
       <c r="N19" t="n">
-        <v>0.053</v>
+        <v>0.4401</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1528</v>
+        <v>-0.2863</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8051</v>
+        <v>0.1348</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0278</v>
+        <v>0.2948</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8329</v>
+        <v>-0.16</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2859</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8173</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9463</v>
+        <v>-0.931</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1289</v>
+        <v>0.1119</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0651</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0248</v>
+        <v>3.2666</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0403</v>
+        <v>-3.3473</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5648</v>
+        <v>0.2454</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0621</v>
+        <v>2.753</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6269</v>
+        <v>-2.5076</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5003</v>
+        <v>-0.3261</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4134</v>
+        <v>-0.8397</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2056</v>
+        <v>-0.5453</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4164</v>
+        <v>-0.4742</v>
       </c>
       <c r="U20" t="n">
-        <v>0.622</v>
+        <v>-0.0711</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8664</v>
+        <v>-1.2517</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.499</v>
+        <v>-1.0984</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3674</v>
+        <v>-0.1533</v>
       </c>
       <c r="G21" t="n">
         <v>0.8905</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1779</v>
+        <v>-0.5632</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0145</v>
+        <v>0.4151</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1924</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.614</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1622</v>
+        <v>-2.1118</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6319</v>
+        <v>-1.9463</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5302</v>
+        <v>-0.1655</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-1.0651</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2666</v>
+        <v>-0.0248</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3473</v>
+        <v>-1.0403</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2454</v>
+        <v>-0.5648</v>
       </c>
       <c r="K22" t="n">
-        <v>2.753</v>
+        <v>0.0621</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.5076</v>
+        <v>-0.6269</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3261</v>
+        <v>-0.5003</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8397</v>
+        <v>-0.4134</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8884</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1752</v>
+        <v>-0.4164</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7131999999999999</v>
+        <v>0.3275</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W22" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.105</v>
+        <v>-3.0584</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1253</v>
+        <v>-2.0252</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9796</v>
+        <v>-1.0332</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9067</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0053</v>
+        <v>0.0413</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1335</v>
+        <v>0.2337</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1388</v>
+        <v>-0.1924</v>
       </c>
       <c r="V23" t="n">
         <v>-1.228</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.716199999999997</v>
+        <v>9.383800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>7.0042</v>
+        <v>7.004100000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>1.712299999999999</v>
+        <v>2.3798</v>
       </c>
       <c r="G24" t="n">
-        <v>5.9414</v>
+        <v>5.941400000000001</v>
       </c>
       <c r="H24" t="n">
         <v>5.941599999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>6.106226635438361e-16</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="J24" t="n">
         <v>7.1727</v>
@@ -2311,7 +2311,7 @@
         <v>-1.2314</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9644</v>
       </c>
       <c r="O24" t="n">
         <v>-2.1957</v>
@@ -2326,13 +2326,13 @@
         <v>13.5104</v>
       </c>
       <c r="S24" t="n">
-        <v>1.414399999999999</v>
+        <v>2.0821</v>
       </c>
       <c r="T24" t="n">
         <v>3.8405</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.426099999999999</v>
+        <v>-1.7586</v>
       </c>
       <c r="V24" t="n">
         <v>4.2556</v>
